--- a/calendar/Calendar.xlsx
+++ b/calendar/Calendar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabehope/Documents/Documents - Mac/Courses/cs152.github.io/calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586F874F-60F6-2840-A1D2-33E9EC141D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8798D11-A369-5143-AE45-21E779FC9C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="1900" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="760" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="151">
   <si>
     <t>Week</t>
   </si>
@@ -1640,6 +1640,9 @@
   </si>
   <si>
     <t xml:space="preserve"> [Notebook](https://drive.google.com/file/d/1N76hpENuKchbfN0o-NZ02FAgZYPiWPVf/view?usp=drive_link) [Notes](../lecture8-regularization/notes.qmd) [Slides](../lecture8-regularization/slides.pdf) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Slides](../lecture9-optimization/slides.pdf) </t>
   </si>
 </sst>
 </file>
@@ -3393,7 +3396,9 @@
       <c r="E22" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F22" s="8"/>
+      <c r="F22" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="G22" s="2" t="s">
         <v>28</v>
       </c>

--- a/calendar/Calendar.xlsx
+++ b/calendar/Calendar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabehope/Documents/Documents - Mac/Courses/cs152.github.io/calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8798D11-A369-5143-AE45-21E779FC9C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B9220A-D287-8F48-95FB-89DF7F7FC94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="760" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="153">
   <si>
     <t>Week</t>
   </si>
@@ -1066,9 +1066,6 @@
     <t>Convolutional Networks</t>
   </si>
   <si>
-    <t>Convolutional Networks (cont.)</t>
-  </si>
-  <si>
     <r>
       <t>[</t>
     </r>
@@ -1643,6 +1640,15 @@
   </si>
   <si>
     <t xml:space="preserve">[Slides](../lecture9-optimization/slides.pdf) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Slides](../lecture9-optimization/initialization_and_adam.pdf) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Slides](../lecture10-normalization/adam_and_normalization_notes.pdf) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Slides](../lecture10-normalization/normalization_notes.pdf) </t>
   </si>
 </sst>
 </file>
@@ -2960,7 +2966,7 @@
         <v>54</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>55</v>
@@ -2986,7 +2992,7 @@
         <v>59</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>60</v>
@@ -3009,7 +3015,7 @@
         <v>59</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>62</v>
@@ -3031,7 +3037,7 @@
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>18</v>
@@ -3054,7 +3060,7 @@
         <v>65</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>66</v>
@@ -3077,7 +3083,7 @@
         <v>68</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3099,7 +3105,7 @@
       <c r="D9" s="8"/>
       <c r="E9" s="5"/>
       <c r="F9" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>51</v>
@@ -3123,7 +3129,7 @@
         <v>70</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>14</v>
@@ -3168,7 +3174,7 @@
       <c r="D12" s="2"/>
       <c r="E12" s="5"/>
       <c r="F12" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>81</v>
@@ -3214,7 +3220,7 @@
         <v>78</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -3236,7 +3242,7 @@
       <c r="D15" s="8"/>
       <c r="E15" s="5"/>
       <c r="F15" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>86</v>
@@ -3276,13 +3282,13 @@
         <v>8</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>84</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>23</v>
@@ -3304,7 +3310,7 @@
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>91</v>
@@ -3322,13 +3328,13 @@
         <v>8</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>87</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>25</v>
@@ -3351,13 +3357,13 @@
         <v>89</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="48" customHeight="1">
@@ -3373,7 +3379,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>94</v>
@@ -3396,9 +3402,6 @@
       <c r="E22" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>150</v>
-      </c>
       <c r="G22" s="2" t="s">
         <v>28</v>
       </c>
@@ -3419,7 +3422,9 @@
       <c r="E23" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="8"/>
+      <c r="F23" s="8" t="s">
+        <v>149</v>
+      </c>
       <c r="G23" s="2" t="s">
         <v>29</v>
       </c>
@@ -3437,10 +3442,10 @@
       <c r="D24" s="2"/>
       <c r="E24" s="5"/>
       <c r="F24" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="48" customHeight="1">
@@ -3471,12 +3476,14 @@
         <v>8</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="F26" s="8"/>
+      <c r="F26" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="G26" s="2" t="s">
         <v>31</v>
       </c>
@@ -3492,12 +3499,14 @@
         <v>8</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="F27" s="8"/>
+      <c r="F27" s="8" t="s">
+        <v>151</v>
+      </c>
       <c r="G27" s="2" t="s">
         <v>32</v>
       </c>
@@ -3515,10 +3524,10 @@
       <c r="D28" s="2"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="48" customHeight="1">
@@ -3532,12 +3541,14 @@
         <v>8</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="F29" s="8"/>
+        <v>101</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>152</v>
+      </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
       </c>
@@ -3553,17 +3564,17 @@
         <v>8</v>
       </c>
       <c r="D30" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="2" t="s">
         <v>35</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="48" customHeight="1">
@@ -3579,10 +3590,10 @@
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H31" s="8"/>
     </row>
@@ -3597,10 +3608,10 @@
         <v>8</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F32" s="8"/>
       <c r="G32" s="2" t="s">
@@ -3618,7 +3629,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="7"/>
@@ -3626,7 +3637,7 @@
         <v>38</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="48" customHeight="1">
@@ -3642,7 +3653,7 @@
       <c r="D34" s="2"/>
       <c r="E34" s="5"/>
       <c r="F34" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>96</v>
@@ -3660,10 +3671,10 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="2" t="s">
@@ -3681,7 +3692,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -3689,7 +3700,7 @@
         <v>41</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="48" customHeight="1">
@@ -3705,10 +3716,10 @@
       <c r="D37" s="2"/>
       <c r="E37" s="5"/>
       <c r="F37" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="48" customHeight="1">
@@ -3722,7 +3733,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -3741,15 +3752,15 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="48" customHeight="1">
@@ -3765,10 +3776,10 @@
       <c r="D40" s="2"/>
       <c r="E40" s="5"/>
       <c r="F40" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="48" customHeight="1">
@@ -3782,7 +3793,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -3801,7 +3812,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -3822,10 +3833,10 @@
       <c r="D43" s="2"/>
       <c r="E43" s="5"/>
       <c r="F43" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="48" customHeight="1">
@@ -3841,7 +3852,7 @@
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>49</v>
@@ -3864,7 +3875,7 @@
         <v>50</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/calendar/Calendar.xlsx
+++ b/calendar/Calendar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabehope/Documents/Documents - Mac/Courses/cs152.github.io/calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B9220A-D287-8F48-95FB-89DF7F7FC94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97AF8B0-1BE8-A048-B1CF-19BFAEEAD254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7460" yWindow="2700" windowWidth="30240" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="154">
   <si>
     <t>Week</t>
   </si>
@@ -1649,6 +1649,9 @@
   </si>
   <si>
     <t xml:space="preserve">[Slides](../lecture10-normalization/normalization_notes.pdf) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Slides](./notes/lecture16.pdf) </t>
   </si>
 </sst>
 </file>
@@ -3569,7 +3572,9 @@
       <c r="E30" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F30" s="8"/>
+      <c r="F30" s="8" t="s">
+        <v>153</v>
+      </c>
       <c r="G30" s="2" t="s">
         <v>35</v>
       </c>

--- a/calendar/Calendar.xlsx
+++ b/calendar/Calendar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabehope/Documents/Documents - Mac/Courses/cs152.github.io/calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97AF8B0-1BE8-A048-B1CF-19BFAEEAD254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4980C1-2F73-2A48-9D98-17EF0C4FF138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7460" yWindow="2700" windowWidth="30240" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2700" windowWidth="30240" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="155">
   <si>
     <t>Week</t>
   </si>
@@ -1652,6 +1652,9 @@
   </si>
   <si>
     <t xml:space="preserve">[Slides](./notes/lecture16.pdf) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Slides](./notes/lecture17.pdf) </t>
   </si>
 </sst>
 </file>
@@ -3681,7 +3684,9 @@
       <c r="E35" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="F35" s="8"/>
+      <c r="F35" s="8" t="s">
+        <v>154</v>
+      </c>
       <c r="G35" s="2" t="s">
         <v>40</v>
       </c>

--- a/calendar/Calendar.xlsx
+++ b/calendar/Calendar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabehope/Documents/Documents - Mac/Courses/cs152.github.io/calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4980C1-2F73-2A48-9D98-17EF0C4FF138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C1E6DE-B475-4548-B9A9-3109A693A6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2700" windowWidth="30240" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6020" yWindow="1340" windowWidth="30240" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="156">
   <si>
     <t>Week</t>
   </si>
@@ -1655,6 +1655,9 @@
   </si>
   <si>
     <t xml:space="preserve">[Slides](./notes/lecture17.pdf) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Slides](../lecture14-transformers/rnn_attention_annotated.pdf) </t>
   </si>
 </sst>
 </file>
@@ -3705,7 +3708,9 @@
         <v>111</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="F36" s="8" t="s">
+        <v>154</v>
+      </c>
       <c r="G36" s="2" t="s">
         <v>41</v>
       </c>
@@ -3746,7 +3751,9 @@
         <v>115</v>
       </c>
       <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="F38" s="8" t="s">
+        <v>155</v>
+      </c>
       <c r="G38" s="2" t="s">
         <v>43</v>
       </c>
@@ -3765,7 +3772,9 @@
         <v>145</v>
       </c>
       <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+      <c r="F39" s="8" t="s">
+        <v>155</v>
+      </c>
       <c r="G39" s="2" t="s">
         <v>116</v>
       </c>

--- a/calendar/Calendar.xlsx
+++ b/calendar/Calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabehope/Documents/Documents - Mac/Courses/cs152.github.io/calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C1E6DE-B475-4548-B9A9-3109A693A6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B07096-AFB8-F145-A0F1-CA7BBF8E7F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6020" yWindow="1340" windowWidth="30240" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1657,7 +1657,7 @@
     <t xml:space="preserve">[Slides](./notes/lecture17.pdf) </t>
   </si>
   <si>
-    <t xml:space="preserve">[Slides](../lecture14-transformers/rnn_attention_annotated.pdf) </t>
+    <t xml:space="preserve">[Slides](../lecture14-transformers/rnns_attention_annotated.pdf) </t>
   </si>
 </sst>
 </file>
